--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E4FA738-C01A-40A4-A80F-AC0F59377952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4361809B-248D-491F-9792-FEF33AF55049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3230,7 +3230,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD667D20-B9BE-4042-8A77-01DA559466B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9D59B1A-F282-4C27-80F4-EF861ED6D111}">
   <dimension ref="B2:AG440"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10283,7 +10283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9016F6-2AA6-4503-9B62-C499B5C5AE5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AF84BF-70CD-487F-98AE-7CB0146F1CB0}">
   <dimension ref="B9:L13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17175,7 +17175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEA59C1-A5AF-47B0-8A26-9475C42CAE63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E170630-0CA5-43ED-AFD6-5FDE27266769}">
   <dimension ref="A1:I135"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56DCBD89-166C-4D04-8F06-A0300B2B43B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C6C5804-75EB-4D21-9A3B-3501952723D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3116,7 +3116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AEE7800-EFE7-4BA1-A88B-C1A308471E7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F12239C-E0D1-4951-B48D-E8A9E87EB4F6}">
   <dimension ref="B2:AG402"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9637,7 +9637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46415AA-B693-4B29-9960-E92E4A1F663C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DD65337-BBCA-44D3-B656-7730403EF4A7}">
   <dimension ref="B9:L13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16529,7 +16529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E324EBD5-0B55-4E9E-B505-4C920ED654C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD197C2B-0AB9-47DA-9FF4-2E3B257166CE}">
   <dimension ref="A1:I135"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
